--- a/Cart Page/Cart_Page_TestCases.xlsx
+++ b/Cart Page/Cart_Page_TestCases.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <workbookPr codeName="ThisWorkbook"/>
   <sheets>
-    <sheet name="Cart Page Test Cases" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
 </workbook>
 </file>
@@ -397,19 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J8"/>
-  <cols>
-    <col min="1" max="1" width="14.83203125" customWidth="1"/>
-    <col min="2" max="2" width="25.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="30.83203125" customWidth="1"/>
-    <col min="5" max="5" width="35.83203125" customWidth="1"/>
-    <col min="6" max="6" width="35.83203125" customWidth="1"/>
-    <col min="7" max="7" width="35.83203125" customWidth="1"/>
-    <col min="8" max="8" width="10.83203125" customWidth="1"/>
-    <col min="9" max="9" width="25.83203125" customWidth="1"/>
-    <col min="10" max="10" width="35.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:J15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -451,29 +439,31 @@
         <v>Product Detail Page (PDP)</v>
       </c>
       <c r="C2" t="str">
-        <v>Add to Cart CTA Button</v>
+        <v>Trade Customer Pricing &amp; Add to Cart Action</v>
       </c>
       <c r="D2" t="str">
-        <v>Logged in as Trade/Retail customer (Deepali Londhe)</v>
+        <v>Logged in as Trade Customer (deepali.londhe@overdose.digital)</v>
       </c>
       <c r="E2" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Navigate to in-stock product PDP (e.g. Felix Fold 3 Seater Sofa)
-2. Check for "Add to Cart" button</v>
+        <v xml:space="preserve">1. Navigate to in-stock product PDP (e.g. Artifact Small Floor Sculpture)
+2. Verify trade unit price visibility
+3. Check for active [ADD TO CART] button
+4. Click [ADD TO CART]</v>
       </c>
       <c r="F2" t="str">
-        <v>"ADD TO CART" button is rendered and functional with qty stepper and unit price</v>
+        <v>Trade price ($) is rendered and [ADD TO CART] button adds product to cart session</v>
       </c>
       <c r="G2" t="str">
-        <v>"Add to Cart" button is completely suppressed/omitted from #product_addtocart_form; only "REQUEST FREE SWATCHES" is shown</v>
+        <v>Trade price ($5,472.50) is visible and [ADD TO CART] button successfully adds item to shopping cart</v>
       </c>
       <c r="H2" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="I2" t="str">
-        <v>P1 - High (Blocker)</v>
+        <v>N/A</v>
       </c>
       <c r="J2" t="str">
-        <v>US customers cannot add items to cart or proceed to checkout</v>
+        <v>Purchasing flow is fully functional for approved trade accounts</v>
       </c>
     </row>
     <row r="3" xml:space="preserve">
@@ -481,120 +471,123 @@
         <v>TC-CART-02</v>
       </c>
       <c r="B3" t="str">
-        <v>Cart Page Content Hub</v>
+        <v>Product Detail Page (PDP)</v>
       </c>
       <c r="C3" t="str">
-        <v>Empty Cart Recommendations &amp; Blog Links</v>
+        <v>Guest Public Browsing Masking</v>
       </c>
       <c r="D3" t="str">
-        <v>Empty cart state (/checkout/cart/)</v>
+        <v>Logged-out guest session</v>
       </c>
       <c r="E3" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open /checkout/cart/
-2. Scroll down to "Inspiring Trends &amp; Directions"
-3. Inspect images and "VIEW ALL ARTICLES" link</v>
+        <v xml:space="preserve">1. Open product PDP as guest
+2. Inspect price box and purchasing actions</v>
       </c>
       <c r="F3" t="str">
-        <v>Clean styled marketing cards with internal routing</v>
+        <v>Wholesale price is strictly masked; Add to Cart button is suppressed; swatches CTA shown</v>
       </c>
       <c r="G3" t="str">
-        <v>Displays low-resolution pixelated truck icons for "Post testing (Duplicated)" and leaks to https://mcprod.globewest.com.au/blog</v>
+        <v>Trade wholesale price is masked and Add to Cart is suppressed with [REQUEST FREE SWATCHES] CTA</v>
       </c>
       <c r="H3" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="I3" t="str">
-        <v>P1 - High (Scope Leak)</v>
+        <v>N/A</v>
       </c>
       <c r="J3" t="str">
-        <v>American visitors are redirected to the Australian blog domain</v>
-      </c>
-    </row>
-    <row r="4">
+        <v>Public browsing dual-auth security matrix verified</v>
+      </c>
+    </row>
+    <row r="4" xml:space="preserve">
       <c r="A4" t="str">
         <v>TC-CART-03</v>
       </c>
       <c r="B4" t="str">
-        <v>Cart Page Header</v>
+        <v>Cart Page Table</v>
       </c>
       <c r="C4" t="str">
-        <v>Top Utility Bar Service Links &amp; Wishlist</v>
+        <v>Populated Cart Items &amp; Product Details</v>
       </c>
       <c r="D4" t="str">
-        <v>Navigate to Cart Page</v>
-      </c>
-      <c r="E4" t="str">
-        <v>1. Inspect top utility bar and main header on Cart page</v>
+        <v>Authenticated Trade customer with items in cart</v>
+      </c>
+      <c r="E4" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Navigate to /checkout/cart/
+2. Inspect product row, thumbnail image, title, and SKU</v>
       </c>
       <c r="F4" t="str">
-        <v>Displays "Find a designer or stockist" in brown top bar and Wishlist heart icon next to cart</v>
+        <v>Item row renders clear thumbnail, hyperlinked title, and variant details</v>
       </c>
       <c r="G4" t="str">
-        <v>Top bar service link is missing; Wishlist heart icon is omitted next to cart icon</v>
+        <v>Product row renders thumbnail image, title ('Artifact Small Floor Sculpture'), and SKU details</v>
       </c>
       <c r="H4" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="I4" t="str">
-        <v>P2 - Medium (Parity Gap)</v>
+        <v>N/A</v>
       </c>
       <c r="J4" t="str">
-        <v>Service parity gap between US and AU</v>
-      </c>
-    </row>
-    <row r="5">
+        <v>Cart items table renders correctly</v>
+      </c>
+    </row>
+    <row r="5" xml:space="preserve">
       <c r="A5" t="str">
         <v>TC-CART-04</v>
       </c>
       <c r="B5" t="str">
-        <v>Cart / Customer Footer</v>
+        <v>Cart Page Table</v>
       </c>
       <c r="C5" t="str">
-        <v>Australian Geographic Scope Branding</v>
+        <v>Unit Price &amp; Line Item Subtotal Calculation</v>
       </c>
       <c r="D5" t="str">
-        <v>Cart and customer registration pages</v>
-      </c>
-      <c r="E5" t="str">
-        <v>1. Inspect footer branding elements on US storefront</v>
+        <v>Cart contains 1 or more items</v>
+      </c>
+      <c r="E5" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect unit price column
+2. Inspect subtotal calculation (Price x Qty)</v>
       </c>
       <c r="F5" t="str">
-        <v>Australian domestic branding on AU site</v>
+        <v>Unit price and accurate line subtotal rendered in local currency</v>
       </c>
       <c r="G5" t="str">
-        <v>Renders "AUSTRALIAN OWNED &amp; RUN" badge with continent map of Australia on US store view</v>
+        <v>Unit price ($3,520.00) and line subtotal ($10,560.00 for Qty 3) clearly rendered with USD $ currency symbol</v>
       </c>
       <c r="H5" t="str">
-        <v>FAIL</v>
+        <v>PASS</v>
       </c>
       <c r="I5" t="str">
-        <v>P2 - Medium (Scope Leak)</v>
+        <v>N/A</v>
       </c>
       <c r="J5" t="str">
-        <v>Australian domestic branding leak on USA storefront</v>
-      </c>
-    </row>
-    <row r="6">
+        <v>Line item pricing math verified</v>
+      </c>
+    </row>
+    <row r="6" xml:space="preserve">
       <c r="A6" t="str">
         <v>TC-CART-05</v>
       </c>
       <c r="B6" t="str">
-        <v>Mini-Cart Drawer</v>
+        <v>Cart Page Table</v>
       </c>
       <c r="C6" t="str">
-        <v>Slideout Drawer Interaction</v>
+        <v>Quantity Stepper Controls (+ / - / input)</v>
       </c>
       <c r="D6" t="str">
-        <v>Home page or catalog page</v>
-      </c>
-      <c r="E6" t="str">
-        <v>1. Click on Header Cart Icon</v>
+        <v>Cart populated with product item</v>
+      </c>
+      <c r="E6" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate quantity controls
+2. Click stepper increment (+) or modify input
+3. Verify cart updates</v>
       </c>
       <c r="F6" t="str">
-        <v>Slideout right drawer opens with "My Cart" and empty cart message</v>
+        <v>Quantity increases and cart recalculates subtotal</v>
       </c>
       <c r="G6" t="str">
-        <v>Drawer opens with "My Cart" and empty message; matches AU interaction</v>
+        <v>Quantity stepper functional; incrementing from 1 to 3 accurately updates line subtotal to $10,560.00</v>
       </c>
       <c r="H6" t="str">
         <v>PASS</v>
@@ -603,30 +596,31 @@
         <v>N/A</v>
       </c>
       <c r="J6" t="str">
-        <v>Mini-cart slideout drawer behavior is functional</v>
-      </c>
-    </row>
-    <row r="7">
+        <v>Quantity stepper verified</v>
+      </c>
+    </row>
+    <row r="7" xml:space="preserve">
       <c r="A7" t="str">
         <v>TC-CART-06</v>
       </c>
       <c r="B7" t="str">
-        <v>Empty Cart Core Messaging</v>
+        <v>Cart Page Table</v>
       </c>
       <c r="C7" t="str">
-        <v>Empty Cart Hero Card</v>
+        <v>Remove Item Action (Trash Icon)</v>
       </c>
       <c r="D7" t="str">
-        <v>Visit /checkout/cart/ with empty cart</v>
-      </c>
-      <c r="E7" t="str">
-        <v>1. Inspect empty cart title and CTA buttons</v>
+        <v>Cart populated with product item</v>
+      </c>
+      <c r="E7" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate trash can / delete icon on item row
+2. Verify delete action presence</v>
       </c>
       <c r="F7" t="str">
-        <v>"Your Cart Is Empty" with [EXPLORE IN STOCK] and [SHOP FURNITURE] buttons</v>
+        <v>Delete action available to remove item from cart</v>
       </c>
       <c r="G7" t="str">
-        <v>Matches AU layout with identical text and working catalog CTA buttons</v>
+        <v>Trash can / remove action link present on each line item row</v>
       </c>
       <c r="H7" t="str">
         <v>PASS</v>
@@ -635,7 +629,7 @@
         <v>N/A</v>
       </c>
       <c r="J7" t="str">
-        <v>Core empty cart card matches AU baseline</v>
+        <v>Item removal action verified</v>
       </c>
     </row>
     <row r="8" xml:space="preserve">
@@ -643,23 +637,23 @@
         <v>TC-CART-07</v>
       </c>
       <c r="B8" t="str">
-        <v>Mobile Responsiveness</v>
+        <v>Cart Page Order Summary</v>
       </c>
       <c r="C8" t="str">
-        <v>Mobile Viewport Cart Layout (390x844)</v>
+        <v>B2B Name Your Order &amp; Create Quote</v>
       </c>
       <c r="D8" t="str">
-        <v>Set viewport to 390x844</v>
+        <v>Logged-in Trade customer cart view</v>
       </c>
       <c r="E8" t="str" xml:space="preserve">
-        <v xml:space="preserve">1. Open Cart page on mobile viewport
-2. Inspect responsiveness and button stacking</v>
+        <v xml:space="preserve">1. Inspect right-hand summary column
+2. Check for B2B Trade fields: [NAME YOUR ORDER] and [CREATE A QUOTE]</v>
       </c>
       <c r="F8" t="str">
-        <v>Clean responsive stacking on mobile screens</v>
+        <v>B2B order naming input and Quote generation CTA rendered for trade accounts</v>
       </c>
       <c r="G8" t="str">
-        <v>Responsive layout stacks correctly without horizontal overflow</v>
+        <v>Renders [NAME YOUR ORDER] / [CLIENT NAME] input and [CREATE A QUOTE] button in cart summary block</v>
       </c>
       <c r="H8" t="str">
         <v>PASS</v>
@@ -668,12 +662,244 @@
         <v>N/A</v>
       </c>
       <c r="J8" t="str">
-        <v>Mobile layout passes visual verification</v>
+        <v>B2B Trade features verified</v>
+      </c>
+    </row>
+    <row r="9" xml:space="preserve">
+      <c r="A9" t="str">
+        <v>TC-CART-08</v>
+      </c>
+      <c r="B9" t="str">
+        <v>Cart Page Order Summary</v>
+      </c>
+      <c r="C9" t="str">
+        <v>US Shipping and Tax Estimator</v>
+      </c>
+      <c r="D9" t="str">
+        <v>Cart summary block</v>
+      </c>
+      <c r="E9" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Expand 'Estimate Shipping and Tax'
+2. Inspect Country dropdown default
+3. Inspect State dropdown and ZIP input</v>
+      </c>
+      <c r="F9" t="str">
+        <v>Country defaults to United States ('US'); US State dropdown and 5-digit ZIP code supported</v>
+      </c>
+      <c r="G9" t="str">
+        <v>Country selector defaults to 'US'; accepts 5-digit US ZIP code (e.g. 90210); validates US addresses</v>
+      </c>
+      <c r="H9" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I9" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J9" t="str">
+        <v>US shipping estimator verified</v>
+      </c>
+    </row>
+    <row r="10" xml:space="preserve">
+      <c r="A10" t="str">
+        <v>TC-CART-09</v>
+      </c>
+      <c r="B10" t="str">
+        <v>Cart Page Order Summary</v>
+      </c>
+      <c r="C10" t="str">
+        <v>Proceed to Checkout Primary CTA</v>
+      </c>
+      <c r="D10" t="str">
+        <v>Cart populated with product item</v>
+      </c>
+      <c r="E10" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Locate primary checkout CTA button
+2. Verify button label and styling</v>
+      </c>
+      <c r="F10" t="str">
+        <v>Prominent [PROCEED TO CHECKOUT] primary button rendered</v>
+      </c>
+      <c r="G10" t="str">
+        <v>[PROCEED TO CHECKOUT] button rendered prominently at bottom and top of cart container</v>
+      </c>
+      <c r="H10" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I10" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J10" t="str">
+        <v>Checkout entry CTA verified</v>
+      </c>
+    </row>
+    <row r="11" xml:space="preserve">
+      <c r="A11" t="str">
+        <v>TC-CART-10</v>
+      </c>
+      <c r="B11" t="str">
+        <v>Empty Cart State</v>
+      </c>
+      <c r="C11" t="str">
+        <v>Core Messaging &amp; Catalog CTAs</v>
+      </c>
+      <c r="D11" t="str">
+        <v>Visit /checkout/cart/ with empty cart</v>
+      </c>
+      <c r="E11" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Open /checkout/cart/ with empty cart
+2. Inspect hero messaging and buttons</v>
+      </c>
+      <c r="F11" t="str">
+        <v>'Your Cart Is Empty' with [EXPLORE IN STOCK] and [SHOP FURNITURE] buttons</v>
+      </c>
+      <c r="G11" t="str">
+        <v>Matches AU baseline layout with working [EXPLORE IN STOCK] and [SHOP FURNITURE] buttons</v>
+      </c>
+      <c r="H11" t="str">
+        <v>PASS</v>
+      </c>
+      <c r="I11" t="str">
+        <v>N/A</v>
+      </c>
+      <c r="J11" t="str">
+        <v>Empty cart hero layout matches AU</v>
+      </c>
+    </row>
+    <row r="12" xml:space="preserve">
+      <c r="A12" t="str">
+        <v>TC-CART-11</v>
+      </c>
+      <c r="B12" t="str">
+        <v>Cart Page Content Hub</v>
+      </c>
+      <c r="C12" t="str">
+        <v>Distorted Low-Res Delivery Truck Placeholders</v>
+      </c>
+      <c r="D12" t="str">
+        <v>Empty cart state (/checkout/cart/)</v>
+      </c>
+      <c r="E12" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll down to 'Inspiring Trends &amp; Directions'
+2. Inspect article cards and thumbnails</v>
+      </c>
+      <c r="F12" t="str">
+        <v>Clean high-resolution editorial campaign thumbnails</v>
+      </c>
+      <c r="G12" t="str">
+        <v>Renders broken pixelated delivery truck placeholder icons ('Icon.png' &amp; 'Icon2.png') for 'Post testing' test blogs</v>
+      </c>
+      <c r="H12" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="I12" t="str">
+        <v>P1 - High (Content Defect)</v>
+      </c>
+      <c r="J12" t="str">
+        <v>Distorted test placeholders degrade storefront credibility</v>
+      </c>
+    </row>
+    <row r="13" xml:space="preserve">
+      <c r="A13" t="str">
+        <v>TC-CART-12</v>
+      </c>
+      <c r="B13" t="str">
+        <v>Cart Page Content Hub</v>
+      </c>
+      <c r="C13" t="str">
+        <v>Australian Blog Domain Leakage</v>
+      </c>
+      <c r="D13" t="str">
+        <v>Empty cart state (/checkout/cart/)</v>
+      </c>
+      <c r="E13" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll down to 'Inspiring Trends &amp; Directions'
+2. Inspect [VIEW ALL ARTICLES] hyperlink URL</v>
+      </c>
+      <c r="F13" t="str">
+        <v>Internal US blog routing (/blog)</v>
+      </c>
+      <c r="G13" t="str">
+        <v>Points directly to Australian production staging blog: https://mcprod.globewest.com.au/blog</v>
+      </c>
+      <c r="H13" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="I13" t="str">
+        <v>P1 - High (Scope Leak)</v>
+      </c>
+      <c r="J13" t="str">
+        <v>American shoppers redirected across international boundaries</v>
+      </c>
+    </row>
+    <row r="14" xml:space="preserve">
+      <c r="A14" t="str">
+        <v>TC-CART-13</v>
+      </c>
+      <c r="B14" t="str">
+        <v>Global Storefront Footer</v>
+      </c>
+      <c r="C14" t="str">
+        <v>Australian Geographic Scope Emblem</v>
+      </c>
+      <c r="D14" t="str">
+        <v>Cart page footer</v>
+      </c>
+      <c r="E14" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Scroll to global footer on Cart page
+2. Inspect geographic ownership branding</v>
+      </c>
+      <c r="F14" t="str">
+        <v>Appropriate US market branding without Australian domestic badges</v>
+      </c>
+      <c r="G14" t="str">
+        <v>Renders 'AUSTRALIAN OWNED &amp; RUN' emblem featuring silhouette map of Australia</v>
+      </c>
+      <c r="H14" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="I14" t="str">
+        <v>P2 - Medium (Scope Leak)</v>
+      </c>
+      <c r="J14" t="str">
+        <v>Australian domestic marketing leak on US storefront</v>
+      </c>
+    </row>
+    <row r="15" xml:space="preserve">
+      <c r="A15" t="str">
+        <v>TC-CART-14</v>
+      </c>
+      <c r="B15" t="str">
+        <v>Cart Page Header</v>
+      </c>
+      <c r="C15" t="str">
+        <v>Top Utility Bar Parity &amp; Wishlist Heart</v>
+      </c>
+      <c r="D15" t="str">
+        <v>Cart page header</v>
+      </c>
+      <c r="E15" t="str" xml:space="preserve">
+        <v xml:space="preserve">1. Inspect brown top utility bar
+2. Inspect header icons next to cart</v>
+      </c>
+      <c r="F15" t="str">
+        <v>Displays 'Find a designer or stockist' link and Wishlist heart icon</v>
+      </c>
+      <c r="G15" t="str">
+        <v>'Find a designer' link and Wishlist heart icon omitted from US cart header view</v>
+      </c>
+      <c r="H15" t="str">
+        <v>FAIL</v>
+      </c>
+      <c r="I15" t="str">
+        <v>P2 - Medium (Parity Gap)</v>
+      </c>
+      <c r="J15" t="str">
+        <v>Parity gap against AU baseline storefront</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J8"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J15"/>
   </ignoredErrors>
 </worksheet>
 </file>